--- a/Tests/Validation/Wheat/data/FAR HYC W19-06-1.xlsx
+++ b/Tests/Validation/Wheat/data/FAR HYC W19-06-1.xlsx
@@ -1,32 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Observed" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observed" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,16 +48,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -417,126 +430,111 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X112"/>
+  <dimension ref="A1:U112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>SimulationName</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Clock.Today</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Phenology.CurrentStageName</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Wheat.SowingData.Cultivar</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Potential</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>NDVIModel.Script.NDVI</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>NDVIModel.Script.NDVI.se</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Wheat.AboveGround.Wt</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Wheat.AboveGround.Wt.se</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Spike.HeadNumber</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Spike.HeadNumber.se</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Leaf.Height</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Leaf.Height.se</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Density</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Density.se</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Wheat.Grain.Moisture</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Wheat.Grain.WaterContent</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Moisture.se</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Protein</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Protein.se</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Screenings</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Screenings.se</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Wt</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Wt.se</t>
         </is>
@@ -555,16 +553,8 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -576,17 +566,14 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>0.835610301898578</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.133135196924022</v>
+      </c>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="n">
-        <v>0.835610301898578</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.133135196924022</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -594,33 +581,25 @@
           <t>FAR HYC W19-06-1PGRNoneCvAccroc</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="3" t="n">
         <v>43690</v>
       </c>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
+      <c r="D3" t="n">
+        <v>0.7775</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.00629152869605896</v>
+      </c>
+      <c r="F3" t="n">
+        <v>328.888888888889</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7775</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.00629152869605896</v>
-      </c>
-      <c r="I3" t="n">
-        <v>328.888888888889</v>
-      </c>
-      <c r="J3" t="n">
         <v>0.11148086624661</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
@@ -632,9 +611,6 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -642,27 +618,19 @@
           <t>FAR HYC W19-06-1PGRNoneCvAccroc</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="3" t="n">
         <v>43713</v>
       </c>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
+      <c r="D4" t="n">
         <v>0.8225</v>
       </c>
-      <c r="H4" t="n">
+      <c r="E4" t="n">
         <v>0.00478713553878168</v>
       </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -676,9 +644,6 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -686,27 +651,19 @@
           <t>FAR HYC W19-06-1PGRNoneCvAccroc</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="3" t="n">
         <v>43739</v>
       </c>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
+      <c r="D5" t="n">
         <v>0.8725000000000001</v>
       </c>
-      <c r="H5" t="n">
+      <c r="E5" t="n">
         <v>0.00478713553878171</v>
       </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -720,9 +677,6 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -730,27 +684,19 @@
           <t>FAR HYC W19-06-1PGRNoneCvAccroc</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="3" t="n">
         <v>43769</v>
       </c>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
+      <c r="D6" t="n">
         <v>0.7975</v>
       </c>
-      <c r="H6" t="n">
+      <c r="E6" t="n">
         <v>0.0047871355387817</v>
       </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -764,9 +710,6 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -774,27 +717,19 @@
           <t>FAR HYC W19-06-1PGRNoneCvAccroc</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="3" t="n">
         <v>43791</v>
       </c>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
+      <c r="D7" t="n">
         <v>0.6325</v>
       </c>
-      <c r="H7" t="n">
+      <c r="E7" t="n">
         <v>0.0110867789130417</v>
       </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -808,9 +743,6 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -818,27 +750,19 @@
           <t>FAR HYC W19-06-1PGRNoneCvAccroc</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="3" t="n">
         <v>43802</v>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
+      <c r="D8" t="n">
         <v>0.55</v>
       </c>
-      <c r="H8" t="n">
+      <c r="E8" t="n">
         <v>0.00577350269189626</v>
       </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -852,9 +776,6 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -862,33 +783,25 @@
           <t>FAR HYC W19-06-1PGRNoneCvAccroc</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="3" t="n">
         <v>43803</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>1050.83333333333</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.03077640640442</v>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="n">
-        <v>1050.83333333333</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.03077640640442</v>
-      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
@@ -896,9 +809,6 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -906,7 +816,7 @@
           <t>FAR HYC W19-06-1PGRNoneCvAccroc</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="3" t="n">
         <v>43833</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -914,23 +824,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
+      <c r="D10" t="n">
         <v>0.1575</v>
       </c>
-      <c r="H10" t="n">
+      <c r="E10" t="n">
         <v>0.0025</v>
       </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -944,9 +846,6 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -954,7 +853,7 @@
           <t>FAR HYC W19-06-1PGRNoneCvAccroc</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="3" t="n">
         <v>43837</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -963,30 +862,22 @@
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>2412.58726439062</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.606954671116637</v>
+      </c>
+      <c r="H11" t="n">
+        <v>597.2222222222219</v>
+      </c>
       <c r="I11" t="n">
-        <v>2412.58726439062</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.606954671116637</v>
-      </c>
-      <c r="K11" t="n">
-        <v>597.2222222222219</v>
-      </c>
-      <c r="L11" t="n">
         <v>12.2180127431161</v>
       </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -996,9 +887,6 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1006,7 +894,7 @@
           <t>FAR HYC W19-06-1PGRNoneCvAccroc</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="3" t="n">
         <v>43860</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -1015,48 +903,37 @@
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>79.313</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.60587154854254</v>
+      </c>
+      <c r="N12" t="n">
+        <v>11.425</v>
+      </c>
       <c r="O12" t="n">
-        <v>79.313</v>
+        <v>0.131497781983829</v>
       </c>
       <c r="P12" t="n">
-        <v>0.60587154854254</v>
+        <v>11.325</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.425</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.131497781983829</v>
-      </c>
-      <c r="S12" t="n">
-        <v>11.325</v>
-      </c>
+        <v>0.446047456369088</v>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
       <c r="T12" t="n">
-        <v>0.446047456369088</v>
-      </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="n">
         <v>980.018760150259</v>
       </c>
-      <c r="X12" t="n">
+      <c r="U12" t="n">
         <v>0.462529731837332</v>
       </c>
     </row>
@@ -1072,21 +949,9 @@
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -1098,17 +963,14 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>1.00784033823579</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.282664715303599</v>
+      </c>
       <c r="T13" t="inlineStr"/>
-      <c r="U13" t="n">
-        <v>1.00784033823579</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.282664715303599</v>
-      </c>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1116,31 +978,19 @@
           <t>FAR HYC W19-06-1PGRSingleCvAccroc</t>
         </is>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="3" t="n">
         <v>43690</v>
       </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
+      <c r="D14" t="n">
         <v>0.7675</v>
       </c>
-      <c r="H14" t="n">
+      <c r="E14" t="n">
         <v>0.0188745860881769</v>
       </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -1154,9 +1004,6 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1164,31 +1011,19 @@
           <t>FAR HYC W19-06-1PGRSingleCvAccroc</t>
         </is>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="3" t="n">
         <v>43713</v>
       </c>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
+      <c r="D15" t="n">
         <v>0.8175</v>
       </c>
-      <c r="H15" t="n">
+      <c r="E15" t="n">
         <v>0.0103077640640441</v>
       </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -1202,9 +1037,6 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1212,31 +1044,19 @@
           <t>FAR HYC W19-06-1PGRSingleCvAccroc</t>
         </is>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="3" t="n">
         <v>43739</v>
       </c>
       <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
+      <c r="D16" t="n">
         <v>0.86</v>
       </c>
-      <c r="H16" t="n">
+      <c r="E16" t="n">
         <v>0.00816496580927727</v>
       </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -1250,9 +1070,6 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1260,31 +1077,19 @@
           <t>FAR HYC W19-06-1PGRSingleCvAccroc</t>
         </is>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="3" t="n">
         <v>43769</v>
       </c>
       <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
+      <c r="D17" t="n">
         <v>0.8025</v>
       </c>
-      <c r="H17" t="n">
+      <c r="E17" t="n">
         <v>0.00249999999999999</v>
       </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -1298,9 +1103,6 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1308,31 +1110,19 @@
           <t>FAR HYC W19-06-1PGRSingleCvAccroc</t>
         </is>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="3" t="n">
         <v>43791</v>
       </c>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
+      <c r="D18" t="n">
         <v>0.65</v>
       </c>
-      <c r="H18" t="n">
+      <c r="E18" t="n">
         <v>0.00707106781186548</v>
       </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -1346,9 +1136,6 @@
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1356,31 +1143,19 @@
           <t>FAR HYC W19-06-1PGRSingleCvAccroc</t>
         </is>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="3" t="n">
         <v>43802</v>
       </c>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
+      <c r="D19" t="n">
         <v>0.555</v>
       </c>
-      <c r="H19" t="n">
+      <c r="E19" t="n">
         <v>0.015545631755148</v>
       </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -1394,9 +1169,6 @@
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1404,37 +1176,25 @@
           <t>FAR HYC W19-06-1PGRSingleCvAccroc</t>
         </is>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="3" t="n">
         <v>43803</v>
       </c>
       <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="J20" t="n">
+        <v>968.333333333333</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.700528900717693</v>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="n">
-        <v>968.333333333333</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.700528900717693</v>
-      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
@@ -1442,9 +1202,6 @@
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1452,7 +1209,7 @@
           <t>FAR HYC W19-06-1PGRSingleCvAccroc</t>
         </is>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="3" t="n">
         <v>43833</v>
       </c>
       <c r="C21" t="inlineStr">
@@ -1460,27 +1217,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
+      <c r="D21" t="n">
         <v>0.15</v>
       </c>
-      <c r="H21" t="n">
+      <c r="E21" t="n">
         <v>0.00912870929175277</v>
       </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -1494,9 +1239,6 @@
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1504,7 +1246,7 @@
           <t>FAR HYC W19-06-1PGRSingleCvAccroc</t>
         </is>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="3" t="n">
         <v>43837</v>
       </c>
       <c r="C22" t="inlineStr">
@@ -1512,35 +1254,23 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>2622.29032574013</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.01408616975267</v>
+      </c>
+      <c r="H22" t="n">
+        <v>638.888888888889</v>
+      </c>
       <c r="I22" t="n">
-        <v>2622.29032574013</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.01408616975267</v>
-      </c>
-      <c r="K22" t="n">
-        <v>638.888888888889</v>
-      </c>
-      <c r="L22" t="n">
         <v>43.9275497794907</v>
       </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -1550,9 +1280,6 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1560,7 +1287,7 @@
           <t>FAR HYC W19-06-1PGRSingleCvAccroc</t>
         </is>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="3" t="n">
         <v>43860</v>
       </c>
       <c r="C23" t="inlineStr">
@@ -1568,53 +1295,38 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="L23" t="n">
+        <v>80.1465</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.36693721079589</v>
+      </c>
+      <c r="N23" t="n">
+        <v>11.3</v>
+      </c>
       <c r="O23" t="n">
-        <v>80.1465</v>
+        <v>0.108012344973464</v>
       </c>
       <c r="P23" t="n">
-        <v>0.36693721079589</v>
+        <v>10.725</v>
       </c>
       <c r="Q23" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0.108012344973464</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10.725</v>
-      </c>
+        <v>0.411045415171284</v>
+      </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
       <c r="T23" t="n">
-        <v>0.411045415171284</v>
-      </c>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="n">
         <v>1106.3181060909</v>
       </c>
-      <c r="X23" t="n">
+      <c r="U23" t="n">
         <v>0.242048581780843</v>
       </c>
     </row>
@@ -1630,21 +1342,9 @@
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Split both</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -1656,17 +1356,14 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
+      <c r="R24" t="n">
+        <v>1.2808142522405</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.259125867149605</v>
+      </c>
       <c r="T24" t="inlineStr"/>
-      <c r="U24" t="n">
-        <v>1.2808142522405</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0.259125867149605</v>
-      </c>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1674,31 +1371,19 @@
           <t>FAR HYC W19-06-1PGRSplit bothCvAccroc</t>
         </is>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="3" t="n">
         <v>43690</v>
       </c>
       <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Split both</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
+      <c r="D25" t="n">
         <v>0.7725</v>
       </c>
-      <c r="H25" t="n">
+      <c r="E25" t="n">
         <v>0.00629152869605896</v>
       </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -1712,9 +1397,6 @@
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1722,31 +1404,19 @@
           <t>FAR HYC W19-06-1PGRSplit bothCvAccroc</t>
         </is>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="3" t="n">
         <v>43713</v>
       </c>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Split both</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
+      <c r="D26" t="n">
         <v>0.8025</v>
       </c>
-      <c r="H26" t="n">
+      <c r="E26" t="n">
         <v>0.00629152869605894</v>
       </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -1760,9 +1430,6 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1770,31 +1437,19 @@
           <t>FAR HYC W19-06-1PGRSplit bothCvAccroc</t>
         </is>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="3" t="n">
         <v>43739</v>
       </c>
       <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Split both</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
+      <c r="D27" t="n">
         <v>0.855</v>
       </c>
-      <c r="H27" t="n">
+      <c r="E27" t="n">
         <v>0.00645497224367903</v>
       </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
@@ -1808,9 +1463,6 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1818,31 +1470,19 @@
           <t>FAR HYC W19-06-1PGRSplit bothCvAccroc</t>
         </is>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="3" t="n">
         <v>43769</v>
       </c>
       <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Split both</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
+      <c r="D28" t="n">
         <v>0.8075</v>
       </c>
-      <c r="H28" t="n">
+      <c r="E28" t="n">
         <v>0.00250000000000001</v>
       </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
@@ -1856,9 +1496,6 @@
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1866,31 +1503,19 @@
           <t>FAR HYC W19-06-1PGRSplit bothCvAccroc</t>
         </is>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="3" t="n">
         <v>43791</v>
       </c>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Split both</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
+      <c r="D29" t="n">
         <v>0.66</v>
       </c>
-      <c r="H29" t="n">
+      <c r="E29" t="n">
         <v>0.00408248290463863</v>
       </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
@@ -1904,9 +1529,6 @@
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1914,31 +1536,19 @@
           <t>FAR HYC W19-06-1PGRSplit bothCvAccroc</t>
         </is>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="3" t="n">
         <v>43802</v>
       </c>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Split both</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
+      <c r="D30" t="n">
         <v>0.57</v>
       </c>
-      <c r="H30" t="n">
+      <c r="E30" t="n">
         <v>0.0040824829046386</v>
       </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
@@ -1952,9 +1562,6 @@
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1962,37 +1569,25 @@
           <t>FAR HYC W19-06-1PGRSplit bothCvAccroc</t>
         </is>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="3" t="n">
         <v>43803</v>
       </c>
       <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Split both</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="J31" t="n">
+        <v>985</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.06718737290547</v>
+      </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="n">
-        <v>985</v>
-      </c>
-      <c r="N31" t="n">
-        <v>1.06718737290547</v>
-      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
@@ -2000,9 +1595,6 @@
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2010,7 +1602,7 @@
           <t>FAR HYC W19-06-1PGRSplit bothCvAccroc</t>
         </is>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="3" t="n">
         <v>43833</v>
       </c>
       <c r="C32" t="inlineStr">
@@ -2018,27 +1610,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Split both</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
+      <c r="D32" t="n">
         <v>0.17</v>
       </c>
-      <c r="H32" t="n">
+      <c r="E32" t="n">
         <v>0.00707106781186548</v>
       </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
@@ -2052,9 +1632,6 @@
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2062,7 +1639,7 @@
           <t>FAR HYC W19-06-1PGRSplit bothCvAccroc</t>
         </is>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="3" t="n">
         <v>43837</v>
       </c>
       <c r="C33" t="inlineStr">
@@ -2070,35 +1647,23 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Split both</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="n">
+        <v>2625.0239797328</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.519038893180866</v>
+      </c>
+      <c r="H33" t="n">
+        <v>616.666666666667</v>
+      </c>
       <c r="I33" t="n">
-        <v>2625.0239797328</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.519038893180866</v>
-      </c>
-      <c r="K33" t="n">
-        <v>616.666666666667</v>
-      </c>
-      <c r="L33" t="n">
         <v>16.8386191432138</v>
       </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
@@ -2108,9 +1673,6 @@
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2118,7 +1680,7 @@
           <t>FAR HYC W19-06-1PGRSplit bothCvAccroc</t>
         </is>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="3" t="n">
         <v>43860</v>
       </c>
       <c r="C34" t="inlineStr">
@@ -2126,53 +1688,38 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Split both</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>78.997</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.15971745886617</v>
+      </c>
+      <c r="N34" t="n">
+        <v>11</v>
+      </c>
       <c r="O34" t="n">
-        <v>78.997</v>
+        <v>0.147196014438798</v>
       </c>
       <c r="P34" t="n">
-        <v>0.15971745886617</v>
+        <v>11.125</v>
       </c>
       <c r="Q34" t="n">
-        <v>11</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0.147196014438798</v>
-      </c>
-      <c r="S34" t="n">
-        <v>11.125</v>
-      </c>
+        <v>0.268871096748361</v>
+      </c>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
       <c r="T34" t="n">
-        <v>0.268871096748361</v>
-      </c>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="n">
         <v>1001.50437933936</v>
       </c>
-      <c r="X34" t="n">
+      <c r="U34" t="n">
         <v>0.24366116711441</v>
       </c>
     </row>
@@ -2188,21 +1735,9 @@
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Split Errex</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
@@ -2214,17 +1749,14 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
+      <c r="R35" t="n">
+        <v>0.725782522310826</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.09679634675700841</v>
+      </c>
       <c r="T35" t="inlineStr"/>
-      <c r="U35" t="n">
-        <v>0.725782522310826</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0.09679634675700841</v>
-      </c>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2232,31 +1764,19 @@
           <t>FAR HYC W19-06-1PGRSplit ErrexCvAccroc</t>
         </is>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="3" t="n">
         <v>43690</v>
       </c>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Split Errex</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
+      <c r="D36" t="n">
         <v>0.7875</v>
       </c>
-      <c r="H36" t="n">
+      <c r="E36" t="n">
         <v>0.00853912563829967</v>
       </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
@@ -2270,9 +1790,6 @@
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2280,31 +1797,19 @@
           <t>FAR HYC W19-06-1PGRSplit ErrexCvAccroc</t>
         </is>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="3" t="n">
         <v>43713</v>
       </c>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Split Errex</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
+      <c r="D37" t="n">
         <v>0.83</v>
       </c>
-      <c r="H37" t="n">
+      <c r="E37" t="n">
         <v>0.01</v>
       </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
@@ -2318,9 +1823,6 @@
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2328,31 +1830,19 @@
           <t>FAR HYC W19-06-1PGRSplit ErrexCvAccroc</t>
         </is>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="3" t="n">
         <v>43739</v>
       </c>
       <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Split Errex</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
+      <c r="D38" t="n">
         <v>0.8725000000000001</v>
       </c>
-      <c r="H38" t="n">
+      <c r="E38" t="n">
         <v>0.00629152869605897</v>
       </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
@@ -2366,9 +1856,6 @@
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2376,31 +1863,19 @@
           <t>FAR HYC W19-06-1PGRSplit ErrexCvAccroc</t>
         </is>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="3" t="n">
         <v>43769</v>
       </c>
       <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Split Errex</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
+      <c r="D39" t="n">
         <v>0.8025</v>
       </c>
-      <c r="H39" t="n">
+      <c r="E39" t="n">
         <v>0.00249999999999999</v>
       </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
@@ -2414,9 +1889,6 @@
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2424,31 +1896,19 @@
           <t>FAR HYC W19-06-1PGRSplit ErrexCvAccroc</t>
         </is>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="3" t="n">
         <v>43791</v>
       </c>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Split Errex</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
+      <c r="D40" t="n">
         <v>0.6375</v>
       </c>
-      <c r="H40" t="n">
+      <c r="E40" t="n">
         <v>0.00749999999999999</v>
       </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
@@ -2462,9 +1922,6 @@
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2472,31 +1929,19 @@
           <t>FAR HYC W19-06-1PGRSplit ErrexCvAccroc</t>
         </is>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="3" t="n">
         <v>43802</v>
       </c>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Split Errex</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
+      <c r="D41" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="H41" t="n">
+      <c r="E41" t="n">
         <v>0.0122474487139159</v>
       </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
@@ -2510,9 +1955,6 @@
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2520,37 +1962,25 @@
           <t>FAR HYC W19-06-1PGRSplit ErrexCvAccroc</t>
         </is>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="3" t="n">
         <v>43803</v>
       </c>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Split Errex</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="J42" t="n">
+        <v>989.166666666667</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.946484724300047</v>
+      </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="n">
-        <v>989.166666666667</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0.946484724300047</v>
-      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
@@ -2558,9 +1988,6 @@
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2568,7 +1995,7 @@
           <t>FAR HYC W19-06-1PGRSplit ErrexCvAccroc</t>
         </is>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="3" t="n">
         <v>43833</v>
       </c>
       <c r="C43" t="inlineStr">
@@ -2576,27 +2003,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Split Errex</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
+      <c r="D43" t="n">
         <v>0.15</v>
       </c>
-      <c r="H43" t="n">
+      <c r="E43" t="n">
         <v>0.00707106781186548</v>
       </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
@@ -2610,9 +2025,6 @@
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2620,7 +2032,7 @@
           <t>FAR HYC W19-06-1PGRSplit ErrexCvAccroc</t>
         </is>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="3" t="n">
         <v>43837</v>
       </c>
       <c r="C44" t="inlineStr">
@@ -2628,35 +2040,23 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Split Errex</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="n">
+        <v>2595.15275634348</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1.15911929228976</v>
+      </c>
+      <c r="H44" t="n">
+        <v>612.7777777777781</v>
+      </c>
       <c r="I44" t="n">
-        <v>2595.15275634348</v>
-      </c>
-      <c r="J44" t="n">
-        <v>1.15911929228976</v>
-      </c>
-      <c r="K44" t="n">
-        <v>612.7777777777781</v>
-      </c>
-      <c r="L44" t="n">
         <v>37.8362836724211</v>
       </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
@@ -2666,9 +2066,6 @@
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2676,7 +2073,7 @@
           <t>FAR HYC W19-06-1PGRSplit ErrexCvAccroc</t>
         </is>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="3" t="n">
         <v>43860</v>
       </c>
       <c r="C45" t="inlineStr">
@@ -2684,53 +2081,38 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Split Errex</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="L45" t="n">
+        <v>80.045</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.340719337089439</v>
+      </c>
+      <c r="N45" t="n">
+        <v>11.4</v>
+      </c>
       <c r="O45" t="n">
-        <v>80.045</v>
+        <v>0.135400640077266</v>
       </c>
       <c r="P45" t="n">
-        <v>0.340719337089439</v>
+        <v>11.375</v>
       </c>
       <c r="Q45" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0.135400640077266</v>
-      </c>
-      <c r="S45" t="n">
-        <v>11.375</v>
-      </c>
+        <v>0.406970514902493</v>
+      </c>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
       <c r="T45" t="n">
-        <v>0.406970514902493</v>
-      </c>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="n">
         <v>1002.36424245117</v>
       </c>
-      <c r="X45" t="n">
+      <c r="U45" t="n">
         <v>0.312486848703102</v>
       </c>
     </row>
@@ -2746,21 +2128,9 @@
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Triple</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
@@ -2772,17 +2142,14 @@
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
+      <c r="R46" t="n">
+        <v>0.838912978869217</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0.103549436554207</v>
+      </c>
       <c r="T46" t="inlineStr"/>
-      <c r="U46" t="n">
-        <v>0.838912978869217</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0.103549436554207</v>
-      </c>
-      <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2790,31 +2157,19 @@
           <t>FAR HYC W19-06-1PGRTripleCvAccroc</t>
         </is>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="3" t="n">
         <v>43690</v>
       </c>
       <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Triple</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
+      <c r="D47" t="n">
         <v>0.785</v>
       </c>
-      <c r="H47" t="n">
+      <c r="E47" t="n">
         <v>0.00645497224367904</v>
       </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -2828,9 +2183,6 @@
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2838,31 +2190,19 @@
           <t>FAR HYC W19-06-1PGRTripleCvAccroc</t>
         </is>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="3" t="n">
         <v>43713</v>
       </c>
       <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Triple</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G48" t="n">
+      <c r="D48" t="n">
         <v>0.8075</v>
       </c>
-      <c r="H48" t="n">
+      <c r="E48" t="n">
         <v>0.0137689263682152</v>
       </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
@@ -2876,9 +2216,6 @@
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2886,31 +2223,19 @@
           <t>FAR HYC W19-06-1PGRTripleCvAccroc</t>
         </is>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="3" t="n">
         <v>43739</v>
       </c>
       <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Triple</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G49" t="n">
+      <c r="D49" t="n">
         <v>0.865</v>
       </c>
-      <c r="H49" t="n">
+      <c r="E49" t="n">
         <v>0.00288675134594814</v>
       </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
@@ -2924,9 +2249,6 @@
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2934,31 +2256,19 @@
           <t>FAR HYC W19-06-1PGRTripleCvAccroc</t>
         </is>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="3" t="n">
         <v>43769</v>
       </c>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Triple</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G50" t="n">
+      <c r="D50" t="n">
         <v>0.8075</v>
       </c>
-      <c r="H50" t="n">
+      <c r="E50" t="n">
         <v>0.00250000000000001</v>
       </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
@@ -2972,9 +2282,6 @@
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2982,31 +2289,19 @@
           <t>FAR HYC W19-06-1PGRTripleCvAccroc</t>
         </is>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="3" t="n">
         <v>43791</v>
       </c>
       <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Triple</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
+      <c r="D51" t="n">
         <v>0.665</v>
       </c>
-      <c r="H51" t="n">
+      <c r="E51" t="n">
         <v>0.00957427107756334</v>
       </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
@@ -3020,9 +2315,6 @@
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3030,31 +2322,19 @@
           <t>FAR HYC W19-06-1PGRTripleCvAccroc</t>
         </is>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="3" t="n">
         <v>43802</v>
       </c>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Triple</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
+      <c r="D52" t="n">
         <v>0.57</v>
       </c>
-      <c r="H52" t="n">
+      <c r="E52" t="n">
         <v>0.009128709291752749</v>
       </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
@@ -3068,9 +2348,6 @@
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3078,37 +2355,25 @@
           <t>FAR HYC W19-06-1PGRTripleCvAccroc</t>
         </is>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="3" t="n">
         <v>43803</v>
       </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Triple</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
+      <c r="J53" t="n">
+        <v>965.833333333333</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1.1496778936986</v>
+      </c>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="n">
-        <v>965.833333333333</v>
-      </c>
-      <c r="N53" t="n">
-        <v>1.1496778936986</v>
-      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
@@ -3116,9 +2381,6 @@
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3126,7 +2388,7 @@
           <t>FAR HYC W19-06-1PGRTripleCvAccroc</t>
         </is>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="3" t="n">
         <v>43833</v>
       </c>
       <c r="C54" t="inlineStr">
@@ -3134,27 +2396,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Triple</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
+      <c r="D54" t="n">
         <v>0.1675</v>
       </c>
-      <c r="H54" t="n">
+      <c r="E54" t="n">
         <v>0.00478713553878169</v>
       </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
@@ -3168,9 +2418,6 @@
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3178,7 +2425,7 @@
           <t>FAR HYC W19-06-1PGRTripleCvAccroc</t>
         </is>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="3" t="n">
         <v>43837</v>
       </c>
       <c r="C55" t="inlineStr">
@@ -3186,35 +2433,23 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Triple</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="n">
+        <v>2616.98169219915</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.539501007767733</v>
+      </c>
+      <c r="H55" t="n">
+        <v>638.888888888889</v>
+      </c>
       <c r="I55" t="n">
-        <v>2616.98169219915</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0.539501007767733</v>
-      </c>
-      <c r="K55" t="n">
-        <v>638.888888888889</v>
-      </c>
-      <c r="L55" t="n">
         <v>19.9897092866869</v>
       </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
@@ -3224,9 +2459,6 @@
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3234,7 +2466,7 @@
           <t>FAR HYC W19-06-1PGRTripleCvAccroc</t>
         </is>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="3" t="n">
         <v>43860</v>
       </c>
       <c r="C56" t="inlineStr">
@@ -3242,53 +2474,38 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Triple</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+      <c r="L56" t="n">
+        <v>79.53749999999999</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.257606126997532</v>
+      </c>
+      <c r="N56" t="n">
+        <v>11.225</v>
+      </c>
       <c r="O56" t="n">
-        <v>79.53749999999999</v>
+        <v>0.179698822107065</v>
       </c>
       <c r="P56" t="n">
-        <v>0.257606126997532</v>
+        <v>11.075</v>
       </c>
       <c r="Q56" t="n">
-        <v>11.225</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0.179698822107065</v>
-      </c>
-      <c r="S56" t="n">
-        <v>11.075</v>
-      </c>
+        <v>0.368272996566406</v>
+      </c>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
       <c r="T56" t="n">
-        <v>0.368272996566406</v>
-      </c>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="n">
         <v>1037.58147021027</v>
       </c>
-      <c r="X56" t="n">
+      <c r="U56" t="n">
         <v>0.322000852000434</v>
       </c>
     </row>
@@ -3305,16 +2522,8 @@
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
@@ -3326,17 +2535,14 @@
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
+      <c r="R57" t="n">
+        <v>1.3918570231295</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0.108301453056735</v>
+      </c>
       <c r="T57" t="inlineStr"/>
-      <c r="U57" t="n">
-        <v>1.3918570231295</v>
-      </c>
-      <c r="V57" t="n">
-        <v>0.108301453056735</v>
-      </c>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3344,29 +2550,21 @@
           <t>FAR HYC W19-06-1PGRNoneCvBennett</t>
         </is>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="3" t="n">
         <v>43678</v>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="n">
+        <v>328.222222222222</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.101628711798037</v>
+      </c>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="n">
-        <v>328.222222222222</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0.101628711798037</v>
-      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
@@ -3378,9 +2576,6 @@
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
-      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3388,27 +2583,19 @@
           <t>FAR HYC W19-06-1PGRNoneCvBennett</t>
         </is>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="3" t="n">
         <v>43690</v>
       </c>
       <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G59" t="n">
+      <c r="D59" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="H59" t="n">
+      <c r="E59" t="n">
         <v>0.00408248290463862</v>
       </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
@@ -3422,9 +2609,6 @@
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
-      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3432,27 +2616,19 @@
           <t>FAR HYC W19-06-1PGRNoneCvBennett</t>
         </is>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="3" t="n">
         <v>43713</v>
       </c>
       <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G60" t="n">
+      <c r="D60" t="n">
         <v>0.8225</v>
       </c>
-      <c r="H60" t="n">
+      <c r="E60" t="n">
         <v>0.008539125638299651</v>
       </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
@@ -3466,9 +2642,6 @@
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
-      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3476,27 +2649,19 @@
           <t>FAR HYC W19-06-1PGRNoneCvBennett</t>
         </is>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="3" t="n">
         <v>43739</v>
       </c>
       <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G61" t="n">
+      <c r="D61" t="n">
         <v>0.885</v>
       </c>
-      <c r="H61" t="n">
+      <c r="E61" t="n">
         <v>0.00288675134594813</v>
       </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
@@ -3510,9 +2675,6 @@
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
-      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3520,27 +2682,19 @@
           <t>FAR HYC W19-06-1PGRNoneCvBennett</t>
         </is>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="3" t="n">
         <v>43769</v>
       </c>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G62" t="n">
+      <c r="D62" t="n">
         <v>0.7875</v>
       </c>
-      <c r="H62" t="n">
+      <c r="E62" t="n">
         <v>0.00853912563829968</v>
       </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
@@ -3554,9 +2708,6 @@
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
-      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3564,27 +2715,19 @@
           <t>FAR HYC W19-06-1PGRNoneCvBennett</t>
         </is>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="3" t="n">
         <v>43791</v>
       </c>
       <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G63" t="n">
+      <c r="D63" t="n">
         <v>0.575</v>
       </c>
-      <c r="H63" t="n">
+      <c r="E63" t="n">
         <v>0.0189296944860009</v>
       </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
@@ -3598,9 +2741,6 @@
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
-      <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3608,27 +2748,19 @@
           <t>FAR HYC W19-06-1PGRNoneCvBennett</t>
         </is>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="3" t="n">
         <v>43802</v>
       </c>
       <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G64" t="n">
+      <c r="D64" t="n">
         <v>0.435</v>
       </c>
-      <c r="H64" t="n">
+      <c r="E64" t="n">
         <v>0.0253311402559511</v>
       </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
@@ -3642,9 +2774,6 @@
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr"/>
-      <c r="X64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3652,33 +2781,25 @@
           <t>FAR HYC W19-06-1PGRNoneCvBennett</t>
         </is>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="3" t="n">
         <v>43803</v>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+      <c r="J65" t="n">
+        <v>1145.83333333333</v>
+      </c>
+      <c r="K65" t="n">
+        <v>2.29482106136921</v>
+      </c>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="n">
-        <v>1145.83333333333</v>
-      </c>
-      <c r="N65" t="n">
-        <v>2.29482106136921</v>
-      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
@@ -3686,9 +2807,6 @@
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr"/>
-      <c r="X65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3696,7 +2814,7 @@
           <t>FAR HYC W19-06-1PGRNoneCvBennett</t>
         </is>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="3" t="n">
         <v>43833</v>
       </c>
       <c r="C66" t="inlineStr">
@@ -3704,23 +2822,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G66" t="n">
+      <c r="D66" t="n">
         <v>0.155</v>
       </c>
-      <c r="H66" t="n">
+      <c r="E66" t="n">
         <v>0.00645497224367903</v>
       </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
@@ -3734,9 +2844,6 @@
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr"/>
-      <c r="X66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3744,7 +2851,7 @@
           <t>FAR HYC W19-06-1PGRNoneCvBennett</t>
         </is>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="3" t="n">
         <v>43837</v>
       </c>
       <c r="C67" t="inlineStr">
@@ -3753,30 +2860,22 @@
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="n">
+        <v>2109.65539607765</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1.10375200325731</v>
+      </c>
+      <c r="H67" t="n">
+        <v>453.888888888889</v>
+      </c>
       <c r="I67" t="n">
-        <v>2109.65539607765</v>
-      </c>
-      <c r="J67" t="n">
-        <v>1.10375200325731</v>
-      </c>
-      <c r="K67" t="n">
-        <v>453.888888888889</v>
-      </c>
-      <c r="L67" t="n">
         <v>23.8888888888889</v>
       </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
@@ -3786,9 +2885,6 @@
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr"/>
-      <c r="X67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3796,7 +2892,7 @@
           <t>FAR HYC W19-06-1PGRNoneCvBennett</t>
         </is>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="3" t="n">
         <v>43860</v>
       </c>
       <c r="C68" t="inlineStr">
@@ -3805,48 +2901,37 @@
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+      <c r="L68" t="n">
+        <v>80.19499999999999</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.311011789701507</v>
+      </c>
+      <c r="N68" t="n">
+        <v>11.7</v>
+      </c>
       <c r="O68" t="n">
-        <v>80.19499999999999</v>
+        <v>0.0408248290463863</v>
       </c>
       <c r="P68" t="n">
-        <v>0.311011789701507</v>
+        <v>11.125</v>
       </c>
       <c r="Q68" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="R68" t="n">
-        <v>0.0408248290463863</v>
-      </c>
-      <c r="S68" t="n">
-        <v>11.125</v>
-      </c>
+        <v>0.0853912563829964</v>
+      </c>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
       <c r="T68" t="n">
-        <v>0.0853912563829964</v>
-      </c>
-      <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr"/>
-      <c r="W68" t="n">
         <v>721.562022269281</v>
       </c>
-      <c r="X68" t="n">
+      <c r="U68" t="n">
         <v>0.231185056610516</v>
       </c>
     </row>
@@ -3862,21 +2947,9 @@
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
@@ -3888,17 +2961,14 @@
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
+      <c r="R69" t="n">
+        <v>1.79808119044609</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0.0662112915589812</v>
+      </c>
       <c r="T69" t="inlineStr"/>
-      <c r="U69" t="n">
-        <v>1.79808119044609</v>
-      </c>
-      <c r="V69" t="n">
-        <v>0.0662112915589812</v>
-      </c>
-      <c r="W69" t="inlineStr"/>
-      <c r="X69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3906,31 +2976,19 @@
           <t>FAR HYC W19-06-1PGRSingleCvBennett</t>
         </is>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="3" t="n">
         <v>43690</v>
       </c>
       <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G70" t="n">
+      <c r="D70" t="n">
         <v>0.8225</v>
       </c>
-      <c r="H70" t="n">
+      <c r="E70" t="n">
         <v>0.00749999999999998</v>
       </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
@@ -3944,9 +3002,6 @@
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr"/>
-      <c r="W70" t="inlineStr"/>
-      <c r="X70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3954,31 +3009,19 @@
           <t>FAR HYC W19-06-1PGRSingleCvBennett</t>
         </is>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="3" t="n">
         <v>43713</v>
       </c>
       <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G71" t="n">
+      <c r="D71" t="n">
         <v>0.8149999999999999</v>
       </c>
-      <c r="H71" t="n">
+      <c r="E71" t="n">
         <v>0.009574271077563361</v>
       </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
@@ -3992,9 +3035,6 @@
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr"/>
-      <c r="W71" t="inlineStr"/>
-      <c r="X71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4002,31 +3042,19 @@
           <t>FAR HYC W19-06-1PGRSingleCvBennett</t>
         </is>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="3" t="n">
         <v>43739</v>
       </c>
       <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G72" t="n">
+      <c r="D72" t="n">
         <v>0.8675</v>
       </c>
-      <c r="H72" t="n">
+      <c r="E72" t="n">
         <v>0.00478713553878171</v>
       </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
@@ -4040,9 +3068,6 @@
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr"/>
-      <c r="W72" t="inlineStr"/>
-      <c r="X72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4050,31 +3075,19 @@
           <t>FAR HYC W19-06-1PGRSingleCvBennett</t>
         </is>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="3" t="n">
         <v>43769</v>
       </c>
       <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G73" t="n">
+      <c r="D73" t="n">
         <v>0.79</v>
       </c>
-      <c r="H73" t="n">
+      <c r="E73" t="n">
         <v>0.00408248290463863</v>
       </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
@@ -4088,9 +3101,6 @@
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
-      <c r="V73" t="inlineStr"/>
-      <c r="W73" t="inlineStr"/>
-      <c r="X73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4098,31 +3108,19 @@
           <t>FAR HYC W19-06-1PGRSingleCvBennett</t>
         </is>
       </c>
-      <c r="B74" s="1" t="n">
+      <c r="B74" s="3" t="n">
         <v>43791</v>
       </c>
       <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G74" t="n">
+      <c r="D74" t="n">
         <v>0.64</v>
       </c>
-      <c r="H74" t="n">
+      <c r="E74" t="n">
         <v>0.0216024689946929</v>
       </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
@@ -4136,9 +3134,6 @@
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr"/>
-      <c r="W74" t="inlineStr"/>
-      <c r="X74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4146,31 +3141,19 @@
           <t>FAR HYC W19-06-1PGRSingleCvBennett</t>
         </is>
       </c>
-      <c r="B75" s="1" t="n">
+      <c r="B75" s="3" t="n">
         <v>43802</v>
       </c>
       <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G75" t="n">
+      <c r="D75" t="n">
         <v>0.545</v>
       </c>
-      <c r="H75" t="n">
+      <c r="E75" t="n">
         <v>0.0221735578260835</v>
       </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
@@ -4184,9 +3167,6 @@
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr"/>
-      <c r="W75" t="inlineStr"/>
-      <c r="X75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4194,37 +3174,25 @@
           <t>FAR HYC W19-06-1PGRSingleCvBennett</t>
         </is>
       </c>
-      <c r="B76" s="1" t="n">
+      <c r="B76" s="3" t="n">
         <v>43803</v>
       </c>
       <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
+      <c r="J76" t="n">
+        <v>1069.16666666667</v>
+      </c>
+      <c r="K76" t="n">
+        <v>7.32622761802492</v>
+      </c>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="n">
-        <v>1069.16666666667</v>
-      </c>
-      <c r="N76" t="n">
-        <v>7.32622761802492</v>
-      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr"/>
@@ -4232,9 +3200,6 @@
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr"/>
-      <c r="V76" t="inlineStr"/>
-      <c r="W76" t="inlineStr"/>
-      <c r="X76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4242,7 +3207,7 @@
           <t>FAR HYC W19-06-1PGRSingleCvBennett</t>
         </is>
       </c>
-      <c r="B77" s="1" t="n">
+      <c r="B77" s="3" t="n">
         <v>43833</v>
       </c>
       <c r="C77" t="inlineStr">
@@ -4250,27 +3215,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G77" t="n">
+      <c r="D77" t="n">
         <v>0.1475</v>
       </c>
-      <c r="H77" t="n">
+      <c r="E77" t="n">
         <v>0.00629152869605895</v>
       </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
@@ -4284,9 +3237,6 @@
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr"/>
-      <c r="V77" t="inlineStr"/>
-      <c r="W77" t="inlineStr"/>
-      <c r="X77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4294,7 +3244,7 @@
           <t>FAR HYC W19-06-1PGRSingleCvBennett</t>
         </is>
       </c>
-      <c r="B78" s="1" t="n">
+      <c r="B78" s="3" t="n">
         <v>43837</v>
       </c>
       <c r="C78" t="inlineStr">
@@ -4302,35 +3252,23 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="n">
+        <v>2290.36647412774</v>
+      </c>
+      <c r="G78" t="n">
+        <v>1.59383941746201</v>
+      </c>
+      <c r="H78" t="n">
+        <v>535</v>
+      </c>
       <c r="I78" t="n">
-        <v>2290.36647412774</v>
-      </c>
-      <c r="J78" t="n">
-        <v>1.59383941746201</v>
-      </c>
-      <c r="K78" t="n">
-        <v>535</v>
-      </c>
-      <c r="L78" t="n">
         <v>26.3151992569723</v>
       </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
@@ -4340,9 +3278,6 @@
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr"/>
-      <c r="W78" t="inlineStr"/>
-      <c r="X78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4350,7 +3285,7 @@
           <t>FAR HYC W19-06-1PGRSingleCvBennett</t>
         </is>
       </c>
-      <c r="B79" s="1" t="n">
+      <c r="B79" s="3" t="n">
         <v>43860</v>
       </c>
       <c r="C79" t="inlineStr">
@@ -4358,53 +3293,38 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+      <c r="L79" t="n">
+        <v>80.8185</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.230839590769578</v>
+      </c>
+      <c r="N79" t="n">
+        <v>11.625</v>
+      </c>
       <c r="O79" t="n">
-        <v>80.8185</v>
+        <v>0.103077640640442</v>
       </c>
       <c r="P79" t="n">
-        <v>0.230839590769578</v>
+        <v>11.35</v>
       </c>
       <c r="Q79" t="n">
-        <v>11.625</v>
-      </c>
-      <c r="R79" t="n">
-        <v>0.103077640640442</v>
-      </c>
-      <c r="S79" t="n">
-        <v>11.35</v>
-      </c>
+        <v>0.16583123951777</v>
+      </c>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
       <c r="T79" t="n">
-        <v>0.16583123951777</v>
-      </c>
-      <c r="U79" t="inlineStr"/>
-      <c r="V79" t="inlineStr"/>
-      <c r="W79" t="n">
         <v>862.84868768542</v>
       </c>
-      <c r="X79" t="n">
+      <c r="U79" t="n">
         <v>0.10982454199614</v>
       </c>
     </row>
@@ -4420,21 +3340,9 @@
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Split both</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
@@ -4446,17 +3354,14 @@
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr"/>
+      <c r="R80" t="n">
+        <v>1.68236286091288</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0.0805387278482724</v>
+      </c>
       <c r="T80" t="inlineStr"/>
-      <c r="U80" t="n">
-        <v>1.68236286091288</v>
-      </c>
-      <c r="V80" t="n">
-        <v>0.0805387278482724</v>
-      </c>
-      <c r="W80" t="inlineStr"/>
-      <c r="X80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4464,31 +3369,19 @@
           <t>FAR HYC W19-06-1PGRSplit bothCvBennett</t>
         </is>
       </c>
-      <c r="B81" s="1" t="n">
+      <c r="B81" s="3" t="n">
         <v>43690</v>
       </c>
       <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Split both</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G81" t="n">
+      <c r="D81" t="n">
         <v>0.8225</v>
       </c>
-      <c r="H81" t="n">
+      <c r="E81" t="n">
         <v>0.00478713553878168</v>
       </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
@@ -4502,9 +3395,6 @@
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr"/>
-      <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
-      <c r="X81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4512,31 +3402,19 @@
           <t>FAR HYC W19-06-1PGRSplit bothCvBennett</t>
         </is>
       </c>
-      <c r="B82" s="1" t="n">
+      <c r="B82" s="3" t="n">
         <v>43713</v>
       </c>
       <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Split both</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G82" t="n">
+      <c r="D82" t="n">
         <v>0.8149999999999999</v>
       </c>
-      <c r="H82" t="n">
+      <c r="E82" t="n">
         <v>0.00645497224367903</v>
       </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
@@ -4550,9 +3428,6 @@
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr"/>
-      <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
-      <c r="X82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4560,31 +3435,19 @@
           <t>FAR HYC W19-06-1PGRSplit bothCvBennett</t>
         </is>
       </c>
-      <c r="B83" s="1" t="n">
+      <c r="B83" s="3" t="n">
         <v>43739</v>
       </c>
       <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Split both</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G83" t="n">
+      <c r="D83" t="n">
         <v>0.865</v>
       </c>
-      <c r="H83" t="n">
+      <c r="E83" t="n">
         <v>0.00645497224367903</v>
       </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
@@ -4598,9 +3461,6 @@
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="inlineStr"/>
       <c r="U83" t="inlineStr"/>
-      <c r="V83" t="inlineStr"/>
-      <c r="W83" t="inlineStr"/>
-      <c r="X83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4608,31 +3468,19 @@
           <t>FAR HYC W19-06-1PGRSplit bothCvBennett</t>
         </is>
       </c>
-      <c r="B84" s="1" t="n">
+      <c r="B84" s="3" t="n">
         <v>43769</v>
       </c>
       <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Split both</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G84" t="n">
+      <c r="D84" t="n">
         <v>0.8025</v>
       </c>
-      <c r="H84" t="n">
+      <c r="E84" t="n">
         <v>0.00249999999999999</v>
       </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
@@ -4646,9 +3494,6 @@
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="inlineStr"/>
       <c r="U84" t="inlineStr"/>
-      <c r="V84" t="inlineStr"/>
-      <c r="W84" t="inlineStr"/>
-      <c r="X84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4656,31 +3501,19 @@
           <t>FAR HYC W19-06-1PGRSplit bothCvBennett</t>
         </is>
       </c>
-      <c r="B85" s="1" t="n">
+      <c r="B85" s="3" t="n">
         <v>43791</v>
       </c>
       <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Split both</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G85" t="n">
+      <c r="D85" t="n">
         <v>0.6625</v>
       </c>
-      <c r="H85" t="n">
+      <c r="E85" t="n">
         <v>0.0125</v>
       </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
@@ -4694,9 +3527,6 @@
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="inlineStr"/>
       <c r="U85" t="inlineStr"/>
-      <c r="V85" t="inlineStr"/>
-      <c r="W85" t="inlineStr"/>
-      <c r="X85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4704,31 +3534,19 @@
           <t>FAR HYC W19-06-1PGRSplit bothCvBennett</t>
         </is>
       </c>
-      <c r="B86" s="1" t="n">
+      <c r="B86" s="3" t="n">
         <v>43802</v>
       </c>
       <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Split both</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G86" t="n">
+      <c r="D86" t="n">
         <v>0.5775</v>
       </c>
-      <c r="H86" t="n">
+      <c r="E86" t="n">
         <v>0.0110867789130417</v>
       </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
@@ -4742,9 +3560,6 @@
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr"/>
-      <c r="V86" t="inlineStr"/>
-      <c r="W86" t="inlineStr"/>
-      <c r="X86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4752,37 +3567,25 @@
           <t>FAR HYC W19-06-1PGRSplit bothCvBennett</t>
         </is>
       </c>
-      <c r="B87" s="1" t="n">
+      <c r="B87" s="3" t="n">
         <v>43803</v>
       </c>
       <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Split both</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
+      <c r="J87" t="n">
+        <v>1148.33333333333</v>
+      </c>
+      <c r="K87" t="n">
+        <v>1.26564286109939</v>
+      </c>
       <c r="L87" t="inlineStr"/>
-      <c r="M87" t="n">
-        <v>1148.33333333333</v>
-      </c>
-      <c r="N87" t="n">
-        <v>1.26564286109939</v>
-      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr"/>
@@ -4790,9 +3593,6 @@
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="inlineStr"/>
       <c r="U87" t="inlineStr"/>
-      <c r="V87" t="inlineStr"/>
-      <c r="W87" t="inlineStr"/>
-      <c r="X87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4800,7 +3600,7 @@
           <t>FAR HYC W19-06-1PGRSplit bothCvBennett</t>
         </is>
       </c>
-      <c r="B88" s="1" t="n">
+      <c r="B88" s="3" t="n">
         <v>43833</v>
       </c>
       <c r="C88" t="inlineStr">
@@ -4808,27 +3608,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Split both</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G88" t="n">
+      <c r="D88" t="n">
         <v>0.155</v>
       </c>
-      <c r="H88" t="n">
+      <c r="E88" t="n">
         <v>0.00288675134594813</v>
       </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
@@ -4842,9 +3630,6 @@
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="inlineStr"/>
       <c r="U88" t="inlineStr"/>
-      <c r="V88" t="inlineStr"/>
-      <c r="W88" t="inlineStr"/>
-      <c r="X88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4852,7 +3637,7 @@
           <t>FAR HYC W19-06-1PGRSplit bothCvBennett</t>
         </is>
       </c>
-      <c r="B89" s="1" t="n">
+      <c r="B89" s="3" t="n">
         <v>43837</v>
       </c>
       <c r="C89" t="inlineStr">
@@ -4860,35 +3645,23 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Split both</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="n">
+        <v>2420.81531323977</v>
+      </c>
+      <c r="G89" t="n">
+        <v>2.34661958760493</v>
+      </c>
+      <c r="H89" t="n">
+        <v>537.7777777777781</v>
+      </c>
       <c r="I89" t="n">
-        <v>2420.81531323977</v>
-      </c>
-      <c r="J89" t="n">
-        <v>2.34661958760493</v>
-      </c>
-      <c r="K89" t="n">
-        <v>537.7777777777781</v>
-      </c>
-      <c r="L89" t="n">
         <v>53.6640977837744</v>
       </c>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
@@ -4898,9 +3671,6 @@
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="inlineStr"/>
       <c r="U89" t="inlineStr"/>
-      <c r="V89" t="inlineStr"/>
-      <c r="W89" t="inlineStr"/>
-      <c r="X89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4908,7 +3678,7 @@
           <t>FAR HYC W19-06-1PGRSplit bothCvBennett</t>
         </is>
       </c>
-      <c r="B90" s="1" t="n">
+      <c r="B90" s="3" t="n">
         <v>43860</v>
       </c>
       <c r="C90" t="inlineStr">
@@ -4916,53 +3686,38 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Split both</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+      <c r="L90" t="n">
+        <v>81.2975</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.149969719165795</v>
+      </c>
+      <c r="N90" t="n">
+        <v>11.7</v>
+      </c>
       <c r="O90" t="n">
-        <v>81.2975</v>
+        <v>0.07071067811865479</v>
       </c>
       <c r="P90" t="n">
-        <v>0.149969719165795</v>
+        <v>11.325</v>
       </c>
       <c r="Q90" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="R90" t="n">
-        <v>0.07071067811865479</v>
-      </c>
-      <c r="S90" t="n">
-        <v>11.325</v>
-      </c>
+        <v>0.265753645318366</v>
+      </c>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr"/>
       <c r="T90" t="n">
-        <v>0.265753645318366</v>
-      </c>
-      <c r="U90" t="inlineStr"/>
-      <c r="V90" t="inlineStr"/>
-      <c r="W90" t="n">
         <v>857.649227880864</v>
       </c>
-      <c r="X90" t="n">
+      <c r="U90" t="n">
         <v>0.0510375513162795</v>
       </c>
     </row>
@@ -4978,21 +3733,9 @@
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Split Errex</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
@@ -5004,17 +3747,14 @@
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr"/>
       <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr"/>
-      <c r="S91" t="inlineStr"/>
+      <c r="R91" t="n">
+        <v>1.49651875954575</v>
+      </c>
+      <c r="S91" t="n">
+        <v>0.160767659842903</v>
+      </c>
       <c r="T91" t="inlineStr"/>
-      <c r="U91" t="n">
-        <v>1.49651875954575</v>
-      </c>
-      <c r="V91" t="n">
-        <v>0.160767659842903</v>
-      </c>
-      <c r="W91" t="inlineStr"/>
-      <c r="X91" t="inlineStr"/>
+      <c r="U91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5022,31 +3762,19 @@
           <t>FAR HYC W19-06-1PGRSplit ErrexCvBennett</t>
         </is>
       </c>
-      <c r="B92" s="1" t="n">
+      <c r="B92" s="3" t="n">
         <v>43690</v>
       </c>
       <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Split Errex</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G92" t="n">
+      <c r="D92" t="n">
         <v>0.8125</v>
       </c>
-      <c r="H92" t="n">
+      <c r="E92" t="n">
         <v>0.00629152869605893</v>
       </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
@@ -5060,9 +3788,6 @@
       <c r="S92" t="inlineStr"/>
       <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr"/>
-      <c r="V92" t="inlineStr"/>
-      <c r="W92" t="inlineStr"/>
-      <c r="X92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5070,31 +3795,19 @@
           <t>FAR HYC W19-06-1PGRSplit ErrexCvBennett</t>
         </is>
       </c>
-      <c r="B93" s="1" t="n">
+      <c r="B93" s="3" t="n">
         <v>43713</v>
       </c>
       <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Split Errex</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G93" t="n">
+      <c r="D93" t="n">
         <v>0.8125</v>
       </c>
-      <c r="H93" t="n">
+      <c r="E93" t="n">
         <v>0.00629152869605895</v>
       </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
@@ -5108,9 +3821,6 @@
       <c r="S93" t="inlineStr"/>
       <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr"/>
-      <c r="V93" t="inlineStr"/>
-      <c r="W93" t="inlineStr"/>
-      <c r="X93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5118,31 +3828,19 @@
           <t>FAR HYC W19-06-1PGRSplit ErrexCvBennett</t>
         </is>
       </c>
-      <c r="B94" s="1" t="n">
+      <c r="B94" s="3" t="n">
         <v>43739</v>
       </c>
       <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Split Errex</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G94" t="n">
+      <c r="D94" t="n">
         <v>0.86</v>
       </c>
-      <c r="H94" t="n">
+      <c r="E94" t="n">
         <v>0.00707106781186548</v>
       </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
@@ -5156,9 +3854,6 @@
       <c r="S94" t="inlineStr"/>
       <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
-      <c r="V94" t="inlineStr"/>
-      <c r="W94" t="inlineStr"/>
-      <c r="X94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5166,31 +3861,19 @@
           <t>FAR HYC W19-06-1PGRSplit ErrexCvBennett</t>
         </is>
       </c>
-      <c r="B95" s="1" t="n">
+      <c r="B95" s="3" t="n">
         <v>43769</v>
       </c>
       <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Split Errex</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G95" t="n">
+      <c r="D95" t="n">
         <v>0.79</v>
       </c>
-      <c r="H95" t="n">
+      <c r="E95" t="n">
         <v>0.00816496580927727</v>
       </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
@@ -5204,9 +3887,6 @@
       <c r="S95" t="inlineStr"/>
       <c r="T95" t="inlineStr"/>
       <c r="U95" t="inlineStr"/>
-      <c r="V95" t="inlineStr"/>
-      <c r="W95" t="inlineStr"/>
-      <c r="X95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5214,31 +3894,19 @@
           <t>FAR HYC W19-06-1PGRSplit ErrexCvBennett</t>
         </is>
       </c>
-      <c r="B96" s="1" t="n">
+      <c r="B96" s="3" t="n">
         <v>43791</v>
       </c>
       <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Split Errex</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G96" t="n">
+      <c r="D96" t="n">
         <v>0.635</v>
       </c>
-      <c r="H96" t="n">
+      <c r="E96" t="n">
         <v>0.0175594229214212</v>
       </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
@@ -5252,9 +3920,6 @@
       <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
-      <c r="V96" t="inlineStr"/>
-      <c r="W96" t="inlineStr"/>
-      <c r="X96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5262,31 +3927,19 @@
           <t>FAR HYC W19-06-1PGRSplit ErrexCvBennett</t>
         </is>
       </c>
-      <c r="B97" s="1" t="n">
+      <c r="B97" s="3" t="n">
         <v>43802</v>
       </c>
       <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Split Errex</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G97" t="n">
+      <c r="D97" t="n">
         <v>0.5525</v>
       </c>
-      <c r="H97" t="n">
+      <c r="E97" t="n">
         <v>0.0228673712233537</v>
       </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
@@ -5300,9 +3953,6 @@
       <c r="S97" t="inlineStr"/>
       <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr"/>
-      <c r="V97" t="inlineStr"/>
-      <c r="W97" t="inlineStr"/>
-      <c r="X97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5310,37 +3960,25 @@
           <t>FAR HYC W19-06-1PGRSplit ErrexCvBennett</t>
         </is>
       </c>
-      <c r="B98" s="1" t="n">
+      <c r="B98" s="3" t="n">
         <v>43803</v>
       </c>
       <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Split Errex</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
+      <c r="J98" t="n">
+        <v>1136.66666666667</v>
+      </c>
+      <c r="K98" t="n">
+        <v>1.67221299369916</v>
+      </c>
       <c r="L98" t="inlineStr"/>
-      <c r="M98" t="n">
-        <v>1136.66666666667</v>
-      </c>
-      <c r="N98" t="n">
-        <v>1.67221299369916</v>
-      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr"/>
       <c r="Q98" t="inlineStr"/>
@@ -5348,9 +3986,6 @@
       <c r="S98" t="inlineStr"/>
       <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr"/>
-      <c r="V98" t="inlineStr"/>
-      <c r="W98" t="inlineStr"/>
-      <c r="X98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5358,7 +3993,7 @@
           <t>FAR HYC W19-06-1PGRSplit ErrexCvBennett</t>
         </is>
       </c>
-      <c r="B99" s="1" t="n">
+      <c r="B99" s="3" t="n">
         <v>43833</v>
       </c>
       <c r="C99" t="inlineStr">
@@ -5366,27 +4001,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Split Errex</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G99" t="n">
+      <c r="D99" t="n">
         <v>0.1475</v>
       </c>
-      <c r="H99" t="n">
+      <c r="E99" t="n">
         <v>0.0025</v>
       </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
@@ -5400,9 +4023,6 @@
       <c r="S99" t="inlineStr"/>
       <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr"/>
-      <c r="V99" t="inlineStr"/>
-      <c r="W99" t="inlineStr"/>
-      <c r="X99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5410,7 +4030,7 @@
           <t>FAR HYC W19-06-1PGRSplit ErrexCvBennett</t>
         </is>
       </c>
-      <c r="B100" s="1" t="n">
+      <c r="B100" s="3" t="n">
         <v>43837</v>
       </c>
       <c r="C100" t="inlineStr">
@@ -5418,35 +4038,23 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Split Errex</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="n">
+        <v>2143.81818233922</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.767327520582889</v>
+      </c>
+      <c r="H100" t="n">
+        <v>482.222222222222</v>
+      </c>
       <c r="I100" t="n">
-        <v>2143.81818233922</v>
-      </c>
-      <c r="J100" t="n">
-        <v>0.767327520582889</v>
-      </c>
-      <c r="K100" t="n">
-        <v>482.222222222222</v>
-      </c>
-      <c r="L100" t="n">
         <v>20.8265421029771</v>
       </c>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
@@ -5456,9 +4064,6 @@
       <c r="S100" t="inlineStr"/>
       <c r="T100" t="inlineStr"/>
       <c r="U100" t="inlineStr"/>
-      <c r="V100" t="inlineStr"/>
-      <c r="W100" t="inlineStr"/>
-      <c r="X100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5466,7 +4071,7 @@
           <t>FAR HYC W19-06-1PGRSplit ErrexCvBennett</t>
         </is>
       </c>
-      <c r="B101" s="1" t="n">
+      <c r="B101" s="3" t="n">
         <v>43860</v>
       </c>
       <c r="C101" t="inlineStr">
@@ -5474,53 +4079,38 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Split Errex</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+      <c r="L101" t="n">
+        <v>81.32550000000001</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.163050861185499</v>
+      </c>
+      <c r="N101" t="n">
+        <v>11.55</v>
+      </c>
       <c r="O101" t="n">
-        <v>81.32550000000001</v>
+        <v>0.0866025403784443</v>
       </c>
       <c r="P101" t="n">
-        <v>0.163050861185499</v>
+        <v>11.025</v>
       </c>
       <c r="Q101" t="n">
-        <v>11.55</v>
-      </c>
-      <c r="R101" t="n">
-        <v>0.0866025403784443</v>
-      </c>
-      <c r="S101" t="n">
-        <v>11.025</v>
-      </c>
+        <v>0.154784796841723</v>
+      </c>
+      <c r="R101" t="inlineStr"/>
+      <c r="S101" t="inlineStr"/>
       <c r="T101" t="n">
-        <v>0.154784796841723</v>
-      </c>
-      <c r="U101" t="inlineStr"/>
-      <c r="V101" t="inlineStr"/>
-      <c r="W101" t="n">
         <v>866.225307161086</v>
       </c>
-      <c r="X101" t="n">
+      <c r="U101" t="n">
         <v>0.176586607770761</v>
       </c>
     </row>
@@ -5536,21 +4126,9 @@
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Triple</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
@@ -5562,17 +4140,14 @@
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr"/>
       <c r="Q102" t="inlineStr"/>
-      <c r="R102" t="inlineStr"/>
-      <c r="S102" t="inlineStr"/>
+      <c r="R102" t="n">
+        <v>1.45969025160108</v>
+      </c>
+      <c r="S102" t="n">
+        <v>0.123274448911401</v>
+      </c>
       <c r="T102" t="inlineStr"/>
-      <c r="U102" t="n">
-        <v>1.45969025160108</v>
-      </c>
-      <c r="V102" t="n">
-        <v>0.123274448911401</v>
-      </c>
-      <c r="W102" t="inlineStr"/>
-      <c r="X102" t="inlineStr"/>
+      <c r="U102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5580,31 +4155,19 @@
           <t>FAR HYC W19-06-1PGRTripleCvBennett</t>
         </is>
       </c>
-      <c r="B103" s="1" t="n">
+      <c r="B103" s="3" t="n">
         <v>43690</v>
       </c>
       <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Triple</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G103" t="n">
+      <c r="D103" t="n">
         <v>0.8</v>
       </c>
-      <c r="H103" t="n">
+      <c r="E103" t="n">
         <v>0.0108012344973464</v>
       </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
@@ -5618,9 +4181,6 @@
       <c r="S103" t="inlineStr"/>
       <c r="T103" t="inlineStr"/>
       <c r="U103" t="inlineStr"/>
-      <c r="V103" t="inlineStr"/>
-      <c r="W103" t="inlineStr"/>
-      <c r="X103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5628,31 +4188,19 @@
           <t>FAR HYC W19-06-1PGRTripleCvBennett</t>
         </is>
       </c>
-      <c r="B104" s="1" t="n">
+      <c r="B104" s="3" t="n">
         <v>43713</v>
       </c>
       <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Triple</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G104" t="n">
+      <c r="D104" t="n">
         <v>0.795</v>
       </c>
-      <c r="H104" t="n">
+      <c r="E104" t="n">
         <v>0.015545631755148</v>
       </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
@@ -5666,9 +4214,6 @@
       <c r="S104" t="inlineStr"/>
       <c r="T104" t="inlineStr"/>
       <c r="U104" t="inlineStr"/>
-      <c r="V104" t="inlineStr"/>
-      <c r="W104" t="inlineStr"/>
-      <c r="X104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5676,31 +4221,19 @@
           <t>FAR HYC W19-06-1PGRTripleCvBennett</t>
         </is>
       </c>
-      <c r="B105" s="1" t="n">
+      <c r="B105" s="3" t="n">
         <v>43739</v>
       </c>
       <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Triple</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G105" t="n">
+      <c r="D105" t="n">
         <v>0.865</v>
       </c>
-      <c r="H105" t="n">
+      <c r="E105" t="n">
         <v>0.00957427107756339</v>
       </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
@@ -5714,9 +4247,6 @@
       <c r="S105" t="inlineStr"/>
       <c r="T105" t="inlineStr"/>
       <c r="U105" t="inlineStr"/>
-      <c r="V105" t="inlineStr"/>
-      <c r="W105" t="inlineStr"/>
-      <c r="X105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5724,31 +4254,19 @@
           <t>FAR HYC W19-06-1PGRTripleCvBennett</t>
         </is>
       </c>
-      <c r="B106" s="1" t="n">
+      <c r="B106" s="3" t="n">
         <v>43769</v>
       </c>
       <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Triple</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G106" t="n">
+      <c r="D106" t="n">
         <v>0.7825</v>
       </c>
-      <c r="H106" t="n">
+      <c r="E106" t="n">
         <v>0.0025</v>
       </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
@@ -5762,9 +4280,6 @@
       <c r="S106" t="inlineStr"/>
       <c r="T106" t="inlineStr"/>
       <c r="U106" t="inlineStr"/>
-      <c r="V106" t="inlineStr"/>
-      <c r="W106" t="inlineStr"/>
-      <c r="X106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5772,31 +4287,19 @@
           <t>FAR HYC W19-06-1PGRTripleCvBennett</t>
         </is>
       </c>
-      <c r="B107" s="1" t="n">
+      <c r="B107" s="3" t="n">
         <v>43791</v>
       </c>
       <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Triple</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G107" t="n">
+      <c r="D107" t="n">
         <v>0.6575</v>
       </c>
-      <c r="H107" t="n">
+      <c r="E107" t="n">
         <v>0.00629152869605896</v>
       </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
@@ -5810,9 +4313,6 @@
       <c r="S107" t="inlineStr"/>
       <c r="T107" t="inlineStr"/>
       <c r="U107" t="inlineStr"/>
-      <c r="V107" t="inlineStr"/>
-      <c r="W107" t="inlineStr"/>
-      <c r="X107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5820,31 +4320,19 @@
           <t>FAR HYC W19-06-1PGRTripleCvBennett</t>
         </is>
       </c>
-      <c r="B108" s="1" t="n">
+      <c r="B108" s="3" t="n">
         <v>43802</v>
       </c>
       <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Triple</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G108" t="n">
+      <c r="D108" t="n">
         <v>0.5649999999999999</v>
       </c>
-      <c r="H108" t="n">
+      <c r="E108" t="n">
         <v>0.0193649167310371</v>
       </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
@@ -5858,9 +4346,6 @@
       <c r="S108" t="inlineStr"/>
       <c r="T108" t="inlineStr"/>
       <c r="U108" t="inlineStr"/>
-      <c r="V108" t="inlineStr"/>
-      <c r="W108" t="inlineStr"/>
-      <c r="X108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5868,37 +4353,25 @@
           <t>FAR HYC W19-06-1PGRTripleCvBennett</t>
         </is>
       </c>
-      <c r="B109" s="1" t="n">
+      <c r="B109" s="3" t="n">
         <v>43803</v>
       </c>
       <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Triple</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
+      <c r="J109" t="n">
+        <v>1131.66666666667</v>
+      </c>
+      <c r="K109" t="n">
+        <v>1.98373011903968</v>
+      </c>
       <c r="L109" t="inlineStr"/>
-      <c r="M109" t="n">
-        <v>1131.66666666667</v>
-      </c>
-      <c r="N109" t="n">
-        <v>1.98373011903968</v>
-      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr"/>
@@ -5906,9 +4379,6 @@
       <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr"/>
       <c r="U109" t="inlineStr"/>
-      <c r="V109" t="inlineStr"/>
-      <c r="W109" t="inlineStr"/>
-      <c r="X109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5916,7 +4386,7 @@
           <t>FAR HYC W19-06-1PGRTripleCvBennett</t>
         </is>
       </c>
-      <c r="B110" s="1" t="n">
+      <c r="B110" s="3" t="n">
         <v>43833</v>
       </c>
       <c r="C110" t="inlineStr">
@@ -5924,27 +4394,15 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Triple</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G110" t="n">
+      <c r="D110" t="n">
         <v>0.1525</v>
       </c>
-      <c r="H110" t="n">
+      <c r="E110" t="n">
         <v>0.00478713553878169</v>
       </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
@@ -5958,9 +4416,6 @@
       <c r="S110" t="inlineStr"/>
       <c r="T110" t="inlineStr"/>
       <c r="U110" t="inlineStr"/>
-      <c r="V110" t="inlineStr"/>
-      <c r="W110" t="inlineStr"/>
-      <c r="X110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5968,7 +4423,7 @@
           <t>FAR HYC W19-06-1PGRTripleCvBennett</t>
         </is>
       </c>
-      <c r="B111" s="1" t="n">
+      <c r="B111" s="3" t="n">
         <v>43837</v>
       </c>
       <c r="C111" t="inlineStr">
@@ -5976,35 +4431,23 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Triple</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="n">
+        <v>2378.66415233786</v>
+      </c>
+      <c r="G111" t="n">
+        <v>1.35903071508473</v>
+      </c>
+      <c r="H111" t="n">
+        <v>512.2222222222219</v>
+      </c>
       <c r="I111" t="n">
-        <v>2378.66415233786</v>
-      </c>
-      <c r="J111" t="n">
-        <v>1.35903071508473</v>
-      </c>
-      <c r="K111" t="n">
-        <v>512.2222222222219</v>
-      </c>
-      <c r="L111" t="n">
         <v>27.822186723442</v>
       </c>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr"/>
@@ -6014,9 +4457,6 @@
       <c r="S111" t="inlineStr"/>
       <c r="T111" t="inlineStr"/>
       <c r="U111" t="inlineStr"/>
-      <c r="V111" t="inlineStr"/>
-      <c r="W111" t="inlineStr"/>
-      <c r="X111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6024,7 +4464,7 @@
           <t>FAR HYC W19-06-1PGRTripleCvBennett</t>
         </is>
       </c>
-      <c r="B112" s="1" t="n">
+      <c r="B112" s="3" t="n">
         <v>43860</v>
       </c>
       <c r="C112" t="inlineStr">
@@ -6032,53 +4472,38 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Triple</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Bennett</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
+      <c r="L112" t="n">
+        <v>81.029</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0.454078187099977</v>
+      </c>
+      <c r="N112" t="n">
+        <v>11.525</v>
+      </c>
       <c r="O112" t="n">
-        <v>81.029</v>
+        <v>0.149303940559741</v>
       </c>
       <c r="P112" t="n">
-        <v>0.454078187099977</v>
+        <v>11.125</v>
       </c>
       <c r="Q112" t="n">
-        <v>11.525</v>
-      </c>
-      <c r="R112" t="n">
-        <v>0.149303940559741</v>
-      </c>
-      <c r="S112" t="n">
-        <v>11.125</v>
-      </c>
+        <v>0.103077640640442</v>
+      </c>
+      <c r="R112" t="inlineStr"/>
+      <c r="S112" t="inlineStr"/>
       <c r="T112" t="n">
-        <v>0.103077640640442</v>
-      </c>
-      <c r="U112" t="inlineStr"/>
-      <c r="V112" t="inlineStr"/>
-      <c r="W112" t="n">
         <v>909.393837526718</v>
       </c>
-      <c r="X112" t="n">
+      <c r="U112" t="n">
         <v>0.144217066005074</v>
       </c>
     </row>
